--- a/leave_request_forms/034_leave_or_remote_work_request_form--leave_request_forms.xlsx
+++ b/leave_request_forms/034_leave_or_remote_work_request_form--leave_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employee_1'}</t>
+          <t>employee_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Employee 1'}</t>
+          <t>Employee 1</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'employee_2'}</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Employee 2'}</t>
+          <t>Employee 2</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'employee_3'}</t>
+          <t>employee_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Employee 3'}</t>
+          <t>Employee 3</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sick_leave'}</t>
+          <t>sick_leave</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sick Leave'}</t>
+          <t>Sick Leave</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'remote_work'}</t>
+          <t>remote_work</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Remote Work'}</t>
+          <t>Remote Work</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'personal/family_leave'}</t>
+          <t>personal/family_leave</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Personal/Family Leave'}</t>
+          <t>Personal/Family Leave</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bereavement_leave'}</t>
+          <t>bereavement_leave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bereavement Leave'}</t>
+          <t>Bereavement Leave</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'family/medical_leave'}</t>
+          <t>family/medical_leave</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Family/Medical Leave'}</t>
+          <t>Family/Medical Leave</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager_approval'}</t>
+          <t>manager_approval</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager Approval'}</t>
+          <t>Manager Approval</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team_lead_approval'}</t>
+          <t>team_lead_approval</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team Lead Approval'}</t>
+          <t>Team Lead Approval</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'director_approval'}</t>
+          <t>director_approval</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Director Approval'}</t>
+          <t>Director Approval</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'On Leave'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approval'}</t>
+          <t>approval</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approval'}</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rejection'}</t>
+          <t>rejection</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Rejection'}</t>
+          <t>Rejection</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
